--- a/control_acceso/reportellegadasDocentes.xlsx
+++ b/control_acceso/reportellegadasDocentes.xlsx
@@ -428,8 +428,8 @@
   <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
@@ -484,19 +484,19 @@
         <v>43510319</v>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E2" t="n">
         <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G2" t="n">
-        <v>40</v>
+        <v>54.55</v>
       </c>
     </row>
     <row r="3">
@@ -509,19 +509,19 @@
         <v>1007357972</v>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G3" t="n">
-        <v>40</v>
+        <v>63.64</v>
       </c>
     </row>
     <row r="4">
@@ -540,13 +540,13 @@
         <v>7</v>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G4" t="n">
-        <v>70</v>
+        <v>63.64</v>
       </c>
     </row>
     <row r="5">
@@ -559,19 +559,19 @@
         <v>1130585935</v>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G5" t="n">
-        <v>70</v>
+        <v>90.91</v>
       </c>
     </row>
     <row r="6">
@@ -584,19 +584,19 @@
         <v>35892304</v>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>3</v>
       </c>
       <c r="F6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G6" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -609,19 +609,19 @@
         <v>1152700731</v>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
         <v>5</v>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G7" t="n">
-        <v>50</v>
+        <v>45.45</v>
       </c>
     </row>
     <row r="8">
@@ -634,19 +634,19 @@
         <v>1001653055</v>
       </c>
       <c r="C8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G8" t="n">
-        <v>10</v>
+        <v>18.18</v>
       </c>
     </row>
     <row r="9">
@@ -659,19 +659,19 @@
         <v>1020474026</v>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G9" t="n">
-        <v>30</v>
+        <v>45.45</v>
       </c>
     </row>
     <row r="10">
@@ -687,16 +687,16 @@
         <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G10" t="n">
-        <v>50</v>
+        <v>81.81999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -712,16 +712,16 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E11" t="n">
         <v>2</v>
       </c>
       <c r="F11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G11" t="n">
-        <v>70</v>
+        <v>72.73</v>
       </c>
     </row>
     <row r="12">
@@ -734,19 +734,19 @@
         <v>43988312</v>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G12" t="n">
-        <v>50</v>
+        <v>36.36</v>
       </c>
     </row>
     <row r="13">
@@ -762,16 +762,16 @@
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G13" t="n">
-        <v>70</v>
+        <v>81.81999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -784,19 +784,19 @@
         <v>1017150695</v>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G14" t="n">
-        <v>40</v>
+        <v>63.64</v>
       </c>
     </row>
     <row r="15">
@@ -812,16 +812,16 @@
         <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G15" t="n">
-        <v>50</v>
+        <v>63.64</v>
       </c>
     </row>
     <row r="16">
@@ -834,19 +834,19 @@
         <v>35600857</v>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G16" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -865,10 +865,10 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -890,10 +890,10 @@
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -909,19 +909,19 @@
         <v>1214719923</v>
       </c>
       <c r="C19" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G19" t="n">
-        <v>20</v>
+        <v>27.27</v>
       </c>
     </row>
     <row r="20">
@@ -934,19 +934,19 @@
         <v>1214746713</v>
       </c>
       <c r="C20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D20" t="n">
         <v>3</v>
       </c>
       <c r="E20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G20" t="n">
-        <v>30</v>
+        <v>27.27</v>
       </c>
     </row>
     <row r="21">
@@ -962,16 +962,16 @@
         <v>2</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G21" t="n">
-        <v>40</v>
+        <v>63.64</v>
       </c>
     </row>
     <row r="22">
@@ -984,16 +984,16 @@
         <v>45522917</v>
       </c>
       <c r="C22" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="F22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1009,19 +1009,19 @@
         <v>1214728621</v>
       </c>
       <c r="C23" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D23" t="n">
         <v>4</v>
       </c>
       <c r="E23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F23" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G23" t="n">
-        <v>40</v>
+        <v>36.36</v>
       </c>
     </row>
     <row r="24">
@@ -1037,16 +1037,16 @@
         <v>7</v>
       </c>
       <c r="D24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E24" t="n">
         <v>1</v>
       </c>
       <c r="F24" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G24" t="n">
-        <v>20</v>
+        <v>27.27</v>
       </c>
     </row>
     <row r="25">
@@ -1059,19 +1059,19 @@
         <v>39288736</v>
       </c>
       <c r="C25" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E25" t="n">
         <v>1</v>
       </c>
       <c r="F25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G25" t="n">
-        <v>50</v>
+        <v>90.91</v>
       </c>
     </row>
     <row r="26">
@@ -1084,19 +1084,19 @@
         <v>1000896049</v>
       </c>
       <c r="C26" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E26" t="n">
         <v>1</v>
       </c>
       <c r="F26" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G26" t="n">
-        <v>20</v>
+        <v>90.91</v>
       </c>
     </row>
     <row r="27">
@@ -1134,7 +1134,7 @@
         <v>1072195151</v>
       </c>
       <c r="C28" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
@@ -1143,7 +1143,7 @@
         <v>2</v>
       </c>
       <c r="F28" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1159,19 +1159,19 @@
         <v>23784084</v>
       </c>
       <c r="C29" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>9.09</v>
       </c>
     </row>
     <row r="30">
@@ -1184,19 +1184,19 @@
         <v>43729496</v>
       </c>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F30" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G30" t="n">
-        <v>50</v>
+        <v>54.55</v>
       </c>
     </row>
     <row r="31">
@@ -1209,19 +1209,19 @@
         <v>43269075</v>
       </c>
       <c r="C31" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F31" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G31" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -1259,19 +1259,19 @@
         <v>44000119</v>
       </c>
       <c r="C33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E33" t="n">
         <v>2</v>
       </c>
       <c r="F33" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G33" t="n">
-        <v>60</v>
+        <v>81.81999999999999</v>
       </c>
     </row>
     <row r="34">
@@ -1284,19 +1284,19 @@
         <v>43873533</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D34" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E34" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F34" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G34" t="n">
-        <v>70</v>
+        <v>81.81999999999999</v>
       </c>
     </row>
     <row r="35">
@@ -1312,16 +1312,16 @@
         <v>5</v>
       </c>
       <c r="D35" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F35" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G35" t="n">
-        <v>20</v>
+        <v>36.36</v>
       </c>
     </row>
   </sheetData>

--- a/control_acceso/reportellegadasDocentes.xlsx
+++ b/control_acceso/reportellegadasDocentes.xlsx
@@ -484,19 +484,19 @@
         <v>43510319</v>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E2" t="n">
         <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G2" t="n">
-        <v>54.55</v>
+        <v>76.92</v>
       </c>
     </row>
     <row r="3">
@@ -512,16 +512,16 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G3" t="n">
-        <v>63.64</v>
+        <v>84.62</v>
       </c>
     </row>
     <row r="4">
@@ -534,19 +534,19 @@
         <v>1017159455</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G4" t="n">
-        <v>63.64</v>
+        <v>84.62</v>
       </c>
     </row>
     <row r="5">
@@ -559,19 +559,19 @@
         <v>1130585935</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G5" t="n">
-        <v>90.91</v>
+        <v>53.85</v>
       </c>
     </row>
     <row r="6">
@@ -584,19 +584,19 @@
         <v>35892304</v>
       </c>
       <c r="C6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>23.08</v>
       </c>
     </row>
     <row r="7">
@@ -612,16 +612,16 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E7" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F7" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G7" t="n">
-        <v>45.45</v>
+        <v>76.92</v>
       </c>
     </row>
     <row r="8">
@@ -634,19 +634,19 @@
         <v>1001653055</v>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G8" t="n">
-        <v>18.18</v>
+        <v>38.46</v>
       </c>
     </row>
     <row r="9">
@@ -659,19 +659,19 @@
         <v>1020474026</v>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G9" t="n">
-        <v>45.45</v>
+        <v>76.92</v>
       </c>
     </row>
     <row r="10">
@@ -684,19 +684,19 @@
         <v>1020452454</v>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G10" t="n">
-        <v>81.81999999999999</v>
+        <v>92.31</v>
       </c>
     </row>
     <row r="11">
@@ -712,16 +712,16 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G11" t="n">
-        <v>72.73</v>
+        <v>84.62</v>
       </c>
     </row>
     <row r="12">
@@ -734,19 +734,19 @@
         <v>43988312</v>
       </c>
       <c r="C12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E12" t="n">
         <v>2</v>
       </c>
       <c r="F12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G12" t="n">
-        <v>36.36</v>
+        <v>53.85</v>
       </c>
     </row>
     <row r="13">
@@ -759,19 +759,19 @@
         <v>1017182465</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G13" t="n">
-        <v>81.81999999999999</v>
+        <v>84.62</v>
       </c>
     </row>
     <row r="14">
@@ -784,19 +784,19 @@
         <v>1017150695</v>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D14" t="n">
         <v>7</v>
       </c>
       <c r="E14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G14" t="n">
-        <v>63.64</v>
+        <v>53.85</v>
       </c>
     </row>
     <row r="15">
@@ -809,19 +809,19 @@
         <v>1216723225</v>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F15" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G15" t="n">
-        <v>63.64</v>
+        <v>76.92</v>
       </c>
     </row>
     <row r="16">
@@ -834,16 +834,16 @@
         <v>35600857</v>
       </c>
       <c r="C16" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F16" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,19 +859,19 @@
         <v>43904557</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E17" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="F17" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>23.08</v>
       </c>
     </row>
     <row r="18">
@@ -884,19 +884,19 @@
         <v>1152209765</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F18" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>15.38</v>
       </c>
     </row>
     <row r="19">
@@ -912,16 +912,16 @@
         <v>6</v>
       </c>
       <c r="D19" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F19" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G19" t="n">
-        <v>27.27</v>
+        <v>46.15</v>
       </c>
     </row>
     <row r="20">
@@ -934,19 +934,19 @@
         <v>1214746713</v>
       </c>
       <c r="C20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E20" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F20" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G20" t="n">
-        <v>27.27</v>
+        <v>53.85</v>
       </c>
     </row>
     <row r="21">
@@ -959,19 +959,19 @@
         <v>1037615240</v>
       </c>
       <c r="C21" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F21" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G21" t="n">
-        <v>63.64</v>
+        <v>7.69</v>
       </c>
     </row>
     <row r="22">
@@ -984,19 +984,19 @@
         <v>45522917</v>
       </c>
       <c r="C22" t="n">
+        <v>12</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" t="n">
         <v>0</v>
       </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>11</v>
-      </c>
       <c r="F22" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>7.69</v>
       </c>
     </row>
     <row r="23">
@@ -1009,19 +1009,19 @@
         <v>1214728621</v>
       </c>
       <c r="C23" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F23" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G23" t="n">
-        <v>36.36</v>
+        <v>38.46</v>
       </c>
     </row>
     <row r="24">
@@ -1034,19 +1034,19 @@
         <v>1128431794</v>
       </c>
       <c r="C24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D24" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E24" t="n">
         <v>1</v>
       </c>
       <c r="F24" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G24" t="n">
-        <v>27.27</v>
+        <v>46.15</v>
       </c>
     </row>
     <row r="25">
@@ -1059,19 +1059,19 @@
         <v>39288736</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E25" t="n">
         <v>1</v>
       </c>
       <c r="F25" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G25" t="n">
-        <v>90.91</v>
+        <v>69.23</v>
       </c>
     </row>
     <row r="26">
@@ -1084,7 +1084,7 @@
         <v>1000896049</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D26" t="n">
         <v>10</v>
@@ -1093,10 +1093,10 @@
         <v>1</v>
       </c>
       <c r="F26" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G26" t="n">
-        <v>90.91</v>
+        <v>76.92</v>
       </c>
     </row>
     <row r="27">
@@ -1109,19 +1109,19 @@
         <v>1152446625</v>
       </c>
       <c r="C27" t="n">
+        <v>5</v>
+      </c>
+      <c r="D27" t="n">
         <v>3</v>
       </c>
-      <c r="D27" t="n">
+      <c r="E27" t="n">
         <v>0</v>
       </c>
-      <c r="E27" t="n">
-        <v>3</v>
-      </c>
       <c r="F27" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="28">
@@ -1134,19 +1134,19 @@
         <v>1072195151</v>
       </c>
       <c r="C28" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E28" t="n">
         <v>2</v>
       </c>
       <c r="F28" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>38.46</v>
       </c>
     </row>
     <row r="29">
@@ -1159,19 +1159,19 @@
         <v>23784084</v>
       </c>
       <c r="C29" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E29" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F29" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G29" t="n">
-        <v>9.09</v>
+        <v>30.77</v>
       </c>
     </row>
     <row r="30">
@@ -1184,19 +1184,19 @@
         <v>43729496</v>
       </c>
       <c r="C30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E30" t="n">
         <v>3</v>
       </c>
       <c r="F30" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G30" t="n">
-        <v>54.55</v>
+        <v>69.23</v>
       </c>
     </row>
     <row r="31">
@@ -1209,19 +1209,19 @@
         <v>43269075</v>
       </c>
       <c r="C31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E31" t="n">
         <v>6</v>
       </c>
       <c r="F31" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>23.08</v>
       </c>
     </row>
     <row r="32">
@@ -1240,10 +1240,10 @@
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F32" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1262,16 +1262,16 @@
         <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="F33" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G33" t="n">
-        <v>81.81999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -1287,16 +1287,16 @@
         <v>1</v>
       </c>
       <c r="D34" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E34" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F34" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G34" t="n">
-        <v>81.81999999999999</v>
+        <v>46.15</v>
       </c>
     </row>
     <row r="35">
@@ -1309,19 +1309,19 @@
         <v>1152701729</v>
       </c>
       <c r="C35" t="n">
+        <v>2</v>
+      </c>
+      <c r="D35" t="n">
+        <v>6</v>
+      </c>
+      <c r="E35" t="n">
         <v>5</v>
       </c>
-      <c r="D35" t="n">
-        <v>4</v>
-      </c>
-      <c r="E35" t="n">
-        <v>2</v>
-      </c>
       <c r="F35" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G35" t="n">
-        <v>36.36</v>
+        <v>46.15</v>
       </c>
     </row>
   </sheetData>
